--- a/data/summary_stats.xlsx
+++ b/data/summary_stats.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,25 +497,65 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>deleted_smoothness_2nd_der</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_entropy</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>created_rmse</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>test_ssim_rmse</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>test_psnr_rmse</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>created_smoothness_2nd_der</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>created_entropy</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>test_ssim_r2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>test_ssim_smoothness_2nd_der</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>test_ssim_entropy</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>test_psnr_r2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>test_psnr_smoothness_2nd_der</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>test_psnr_entropy</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>cumulative_deletions</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>cumulative_creations</t>
         </is>
@@ -524,7 +564,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>mcmc</t>
+          <t>MCMC</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -556,18 +596,42 @@
         <v>6141.698393558059</v>
       </c>
       <c r="J2" t="n">
+        <v>1034.048192771084</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.327981054151095</v>
+      </c>
+      <c r="L2" t="n">
         <v>5805.393625157601</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.01309007828410687</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5757305505361301</v>
-      </c>
       <c r="M2" t="n">
+        <v>1055.048192771084</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.346207714960046</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.896613116019969</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.004383236847140573</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4877682078976373</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.9416605732908219</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2523993722359492</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8661956446935979</v>
+      </c>
+      <c r="U2" t="n">
         <v>380884</v>
       </c>
-      <c r="N2" t="n">
+      <c r="V2" t="n">
         <v>386113</v>
       </c>
     </row>
@@ -602,18 +666,42 @@
         <v>2648.057663686133</v>
       </c>
       <c r="J3" t="n">
+        <v>395.6987951807229</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.835101177330776</v>
+      </c>
+      <c r="L3" t="n">
         <v>4709.520879274205</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.006418438830224193</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4141798253257574</v>
-      </c>
       <c r="M3" t="n">
+        <v>701.0240963855422</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.403179561236337</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9855457717329266</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.004197033968838778</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.261470945631549</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.909682910812426</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1604478749219315</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7842439519382248</v>
+      </c>
+      <c r="U3" t="n">
         <v>141490</v>
       </c>
-      <c r="N3" t="n">
+      <c r="V3" t="n">
         <v>227297</v>
       </c>
     </row>
@@ -648,18 +736,42 @@
         <v>3485.988505899557</v>
       </c>
       <c r="J4" t="n">
+        <v>602.2650602409639</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.69967531752425</v>
+      </c>
+      <c r="L4" t="n">
         <v>3485.988505899557</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.006695909288900138</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2871132715674741</v>
-      </c>
       <c r="M4" t="n">
+        <v>602.2650602409639</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.69967531752425</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9689161295316772</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.003189127553593029</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.109509792162714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9497354497342855</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1278184537896127</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.002613570324627</v>
+      </c>
+      <c r="U4" t="n">
         <v>226523</v>
       </c>
-      <c r="N4" t="n">
+      <c r="V4" t="n">
         <v>226523</v>
       </c>
     </row>
@@ -694,18 +806,42 @@
         <v>10534.38398478261</v>
       </c>
       <c r="J5" t="n">
+        <v>3319.21686746988</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.33600510650723</v>
+      </c>
+      <c r="L5" t="n">
         <v>18851.94420580588</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.0138196554321109</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.6240708653859012</v>
-      </c>
       <c r="M5" t="n">
+        <v>4225.654618473895</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.677864263390478</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9053335702568635</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.005022256889126517</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8173359194621734</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9435387271155943</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.29505797141237</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.058974482069527</v>
+      </c>
+      <c r="U5" t="n">
         <v>1181343</v>
       </c>
-      <c r="N5" t="n">
+      <c r="V5" t="n">
         <v>1480951</v>
       </c>
     </row>
@@ -740,18 +876,42 @@
         <v>5358.790719437538</v>
       </c>
       <c r="J6" t="n">
+        <v>1239.746987951807</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.13164987796267</v>
+      </c>
+      <c r="L6" t="n">
         <v>28305.88953753364</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.006248729193672732</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4046676667606738</v>
-      </c>
       <c r="M6" t="n">
+        <v>2258.710843373494</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.73056290273389</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.9937116104835511</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.005908518690954555</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.962801729897439</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9492399540915726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1973784003745422</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.136600135878373</v>
+      </c>
+      <c r="U6" t="n">
         <v>447356</v>
       </c>
-      <c r="N6" t="n">
+      <c r="V6" t="n">
         <v>827542</v>
       </c>
     </row>
@@ -786,18 +946,42 @@
         <v>8541.999078656145</v>
       </c>
       <c r="J7" t="n">
+        <v>1908.911646586345</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.344927256441955</v>
+      </c>
+      <c r="L7" t="n">
         <v>12753.8939579952</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.007632988723885224</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3035433013721014</v>
-      </c>
       <c r="M7" t="n">
+        <v>2800.144578313253</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.405668042504395</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9704764907185311</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.003673924641175704</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.063917751264305</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9607319879791789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.146738020213027</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.058974482069528</v>
+      </c>
+      <c r="U7" t="n">
         <v>770699</v>
       </c>
-      <c r="N7" t="n">
+      <c r="V7" t="n">
         <v>1046894</v>
       </c>
     </row>
@@ -832,18 +1016,42 @@
         <v>21238.56827817494</v>
       </c>
       <c r="J8" t="n">
+        <v>7796.497991967872</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.899675309488097</v>
+      </c>
+      <c r="L8" t="n">
         <v>81603.74304569358</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.01385064431130972</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6270272865956568</v>
-      </c>
       <c r="M8" t="n">
+        <v>10430.5983935743</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.50970858546874</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9137263164601187</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.004500942474061792</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6158699451949977</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9496430512945349</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2786643326830122</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9153205904394861</v>
+      </c>
+      <c r="U8" t="n">
         <v>2889611</v>
       </c>
-      <c r="N8" t="n">
+      <c r="V8" t="n">
         <v>3870119</v>
       </c>
     </row>
@@ -878,18 +1086,42 @@
         <v>16903.35899974135</v>
       </c>
       <c r="J9" t="n">
+        <v>2758.81124497992</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.154280648525629</v>
+      </c>
+      <c r="L9" t="n">
         <v>66080.18736840162</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.007100466334790914</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4159991364844766</v>
-      </c>
       <c r="M9" t="n">
+        <v>5843.457831325301</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.148837481348778</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9944056112482716</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.006344394250349565</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.223901000328937</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9606529403476025</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2098092914483193</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.373222517492973</v>
+      </c>
+      <c r="U9" t="n">
         <v>1064373</v>
       </c>
-      <c r="N9" t="n">
+      <c r="V9" t="n">
         <v>2125459</v>
       </c>
     </row>
@@ -924,25 +1156,49 @@
         <v>14870.80871119583</v>
       </c>
       <c r="J10" t="n">
+        <v>5260.064257028112</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.744965453516751</v>
+      </c>
+      <c r="L10" t="n">
         <v>69054.19200238682</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.007098866042483614</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2966185623089668</v>
-      </c>
       <c r="M10" t="n">
+        <v>7329.180722891566</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.802626541194088</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9799148390192181</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.004312753000042655</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.169921706574328</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9709276867273908</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1666713858905589</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.595989092705214</v>
+      </c>
+      <c r="U10" t="n">
         <v>2071854</v>
       </c>
-      <c r="N10" t="n">
+      <c r="V10" t="n">
         <v>3028949</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -974,18 +1230,42 @@
         <v>2175.606037457764</v>
       </c>
       <c r="J11" t="n">
+        <v>225.0441767068273</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.753353823844399</v>
+      </c>
+      <c r="L11" t="n">
         <v>1930.131945367044</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.01541213403949981</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7489178945565103</v>
-      </c>
       <c r="M11" t="n">
+        <v>249.0361445783132</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.483588265097667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8249217598817079</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.004786994646896015</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8482897116213136</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8936324657206979</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4141506554137346</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.335431539941052</v>
+      </c>
+      <c r="U11" t="n">
         <v>86161</v>
       </c>
-      <c r="N11" t="n">
+      <c r="V11" t="n">
         <v>91083</v>
       </c>
     </row>
@@ -1020,18 +1300,42 @@
         <v>2031.756140406939</v>
       </c>
       <c r="J12" t="n">
+        <v>395.7831325301205</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.436521162408487</v>
+      </c>
+      <c r="L12" t="n">
         <v>6410.186379290328</v>
       </c>
-      <c r="K12" t="n">
-        <v>0.01004255306352244</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4715338009676175</v>
-      </c>
       <c r="M12" t="n">
+        <v>625.4979919678715</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8133626892973141</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9455081763776403</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.006133284758437763</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.925941474869504</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8723585946631037</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2429821178245772</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.459315083207419</v>
+      </c>
+      <c r="U12" t="n">
         <v>150504</v>
       </c>
-      <c r="N12" t="n">
+      <c r="V12" t="n">
         <v>235615</v>
       </c>
     </row>
@@ -1066,18 +1370,42 @@
         <v>2771.588914551029</v>
       </c>
       <c r="J13" t="n">
+        <v>385.5020080321285</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.830333698314948</v>
+      </c>
+      <c r="L13" t="n">
         <v>2818.074361294391</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.007953524325865198</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4195418544649863</v>
-      </c>
       <c r="M13" t="n">
+        <v>388.9558232931727</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.861675709802771</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9385288888874345</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.003928244791247628</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.062652402168277</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8909939045478963</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2339767985509338</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.381932446030796</v>
+      </c>
+      <c r="U13" t="n">
         <v>132039</v>
       </c>
-      <c r="N13" t="n">
+      <c r="V13" t="n">
         <v>131494</v>
       </c>
     </row>
@@ -1112,18 +1440,42 @@
         <v>2505.980348419693</v>
       </c>
       <c r="J14" t="n">
+        <v>421.7791164658635</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.641105166625521</v>
+      </c>
+      <c r="L14" t="n">
         <v>18305.17226262641</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.01518896494558943</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.7366647559573057</v>
-      </c>
       <c r="M14" t="n">
+        <v>1366.313253012048</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.014743056775637</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8577730718625001</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.004741565747694535</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.6158699451949978</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.9168359540483086</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3518077223858937</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.296328675756544</v>
+      </c>
+      <c r="U14" t="n">
         <v>141072</v>
       </c>
-      <c r="N14" t="n">
+      <c r="V14" t="n">
         <v>439980</v>
       </c>
     </row>
@@ -1158,18 +1510,42 @@
         <v>4416.11292369328</v>
       </c>
       <c r="J15" t="n">
+        <v>676.1566265060241</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.624379678715355</v>
+      </c>
+      <c r="L15" t="n">
         <v>25687.48363129692</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.008040939578323683</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3691350800212906</v>
-      </c>
       <c r="M15" t="n">
+        <v>1685.265060240964</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8641316263807789</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9836090152818259</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.006488615816289728</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.131722912583576</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.951253315766697</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.220880485964164</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.702032234414805</v>
+      </c>
+      <c r="U15" t="n">
         <v>246578</v>
       </c>
-      <c r="N15" t="n">
+      <c r="V15" t="n">
         <v>625629</v>
       </c>
     </row>
@@ -1204,18 +1580,42 @@
         <v>3427.974342304509</v>
       </c>
       <c r="J16" t="n">
+        <v>518.9638554216867</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.792216711950142</v>
+      </c>
+      <c r="L16" t="n">
         <v>24132.51023664979</v>
       </c>
-      <c r="K16" t="n">
-        <v>0.01008115398720013</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4108771047766872</v>
-      </c>
       <c r="M16" t="n">
+        <v>1346.016064257028</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.000934664839598</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.9328075923448947</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.004640696400945837</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.089587725319564</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.903973538924167</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2138076533683748</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.393547906417553</v>
+      </c>
+      <c r="U16" t="n">
         <v>178513</v>
       </c>
-      <c r="N16" t="n">
+      <c r="V16" t="n">
         <v>453880</v>
       </c>
     </row>
@@ -1250,18 +1650,42 @@
         <v>2290.764103932394</v>
       </c>
       <c r="J17" t="n">
+        <v>652.144578313253</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.846692608462541</v>
+      </c>
+      <c r="L17" t="n">
         <v>25044.67267963279</v>
       </c>
-      <c r="K17" t="n">
-        <v>0.01449866270452589</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.6695957555587255</v>
-      </c>
       <c r="M17" t="n">
+        <v>3200.690763052209</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.47554382202732</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8822298376875537</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.004929442974654111</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6807418850002293</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9386104796780734</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3452338500946361</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.190870733270284</v>
+      </c>
+      <c r="U17" t="n">
         <v>232825</v>
       </c>
-      <c r="N17" t="n">
+      <c r="V17" t="n">
         <v>1211924</v>
       </c>
     </row>
@@ -1296,18 +1720,42 @@
         <v>2902.896514503192</v>
       </c>
       <c r="J18" t="n">
+        <v>901.0321285140562</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.060818072841416</v>
+      </c>
+      <c r="L18" t="n">
         <v>51573.85253128638</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.005851340458198414</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.3174393928076225</v>
-      </c>
       <c r="M18" t="n">
+        <v>3099.514056224899</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6470017292431518</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9947800664479793</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.007531078701669519</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.398002946072883</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9760470983677541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2486671364763707</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.693953127308007</v>
+      </c>
+      <c r="U18" t="n">
         <v>319874</v>
       </c>
-      <c r="N18" t="n">
+      <c r="V18" t="n">
         <v>1379265</v>
       </c>
     </row>
@@ -1342,25 +1790,49 @@
         <v>2637.130895658125</v>
       </c>
       <c r="J19" t="n">
+        <v>842.0803212851406</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.310614762734669</v>
+      </c>
+      <c r="L19" t="n">
         <v>53029.14127088679</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.008306638961221094</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.319728751084758</v>
-      </c>
       <c r="M19" t="n">
+        <v>3392.429718875502</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.052473902137279</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.9636685987589606</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.004438826306299729</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.376061588276349</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.9554342010539173</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1931724929068078</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.635041883288187</v>
+      </c>
+      <c r="U19" t="n">
         <v>278415</v>
       </c>
-      <c r="N19" t="n">
+      <c r="V19" t="n">
         <v>1234119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>mini_splatting</t>
+          <t>Mini-Splatting</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -1392,18 +1864,42 @@
         <v>11512.88874682118</v>
       </c>
       <c r="J20" t="n">
+        <v>579.8032128514056</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.026883900107042</v>
+      </c>
+      <c r="L20" t="n">
         <v>10956.85388102526</v>
       </c>
-      <c r="K20" t="n">
-        <v>0.01422552103399166</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7246323383611281</v>
-      </c>
       <c r="M20" t="n">
+        <v>497.9598393574297</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.127507500702487</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4087674332559328</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.007405230944806879</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.323669474825893</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5583371692384291</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4560892037300522</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.415035181396649</v>
+      </c>
+      <c r="U20" t="n">
         <v>149315</v>
       </c>
-      <c r="N20" t="n">
+      <c r="V20" t="n">
         <v>154525</v>
       </c>
     </row>
@@ -1438,18 +1934,42 @@
         <v>12122.7239821033</v>
       </c>
       <c r="J21" t="n">
+        <v>744.570281124498</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3393510739758061</v>
+      </c>
+      <c r="L21" t="n">
         <v>11585.82965913915</v>
       </c>
-      <c r="K21" t="n">
-        <v>0.02621949608435504</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4099343567299303</v>
-      </c>
       <c r="M21" t="n">
+        <v>891.5783132530121</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5137617164214141</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3463787120324232</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.01215943863446062</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.653708570996736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2012825522889838</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2257063564929095</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.859231503321268</v>
+      </c>
+      <c r="U21" t="n">
         <v>205987</v>
       </c>
-      <c r="N21" t="n">
+      <c r="V21" t="n">
         <v>291644</v>
       </c>
     </row>
@@ -1484,18 +2004,42 @@
         <v>11540.31425542954</v>
       </c>
       <c r="J22" t="n">
+        <v>647.7831325301205</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3701591740076801</v>
+      </c>
+      <c r="L22" t="n">
         <v>10944.26725680796</v>
       </c>
-      <c r="K22" t="n">
-        <v>0.01862703857541715</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.3683677944098911</v>
-      </c>
       <c r="M22" t="n">
+        <v>568.7670682730924</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.066285229542709</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2876274935274331</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.009513189169493589</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.180893884069721</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.5846123572714808</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2204677503217351</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.502448228882073</v>
+      </c>
+      <c r="U22" t="n">
         <v>178211</v>
       </c>
-      <c r="N22" t="n">
+      <c r="V22" t="n">
         <v>178113</v>
       </c>
     </row>
@@ -1530,18 +2074,42 @@
         <v>44004.26590472918</v>
       </c>
       <c r="J23" t="n">
+        <v>2154.937751004016</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.018886937819119</v>
+      </c>
+      <c r="L23" t="n">
         <v>39640.42336834058</v>
       </c>
-      <c r="K23" t="n">
-        <v>0.01206186333959704</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.666164324862463</v>
-      </c>
       <c r="M23" t="n">
+        <v>2600.325301204819</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5345802176543979</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5908194070847191</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.006702742116017775</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.132939304532188</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.683608934563892</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.416389724313518</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.639627411455038</v>
+      </c>
+      <c r="U23" t="n">
         <v>547294</v>
       </c>
-      <c r="N23" t="n">
+      <c r="V23" t="n">
         <v>846762</v>
       </c>
     </row>
@@ -1576,18 +2144,42 @@
         <v>39929.13480823796</v>
       </c>
       <c r="J24" t="n">
+        <v>2295.485943775101</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.038374174744523</v>
+      </c>
+      <c r="L24" t="n">
         <v>39352.63714530187</v>
       </c>
-      <c r="K24" t="n">
-        <v>0.02745757447128524</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.409455651405987</v>
-      </c>
       <c r="M24" t="n">
+        <v>2889.144578313253</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5677530688311629</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.6490608421520287</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.01383708993142301</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.410771244572472</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.6291066407924961</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2308373031291095</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.722757025162561</v>
+      </c>
+      <c r="U24" t="n">
         <v>621438</v>
       </c>
-      <c r="N24" t="n">
+      <c r="V24" t="n">
         <v>1001283</v>
       </c>
     </row>
@@ -1622,18 +2214,42 @@
         <v>44499.7369363977</v>
       </c>
       <c r="J25" t="n">
+        <v>2171.971887550201</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.022161625860627</v>
+      </c>
+      <c r="L25" t="n">
         <v>41508.82070467743</v>
       </c>
-      <c r="K25" t="n">
-        <v>0.0173603449437445</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.3742339250061642</v>
-      </c>
       <c r="M25" t="n">
+        <v>2836.096385542169</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.241760985117127</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5743414832557822</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.009956336156888441</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.376061588276347</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.5843462396802728</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2403556284579363</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.944147850699604</v>
+      </c>
+      <c r="U25" t="n">
         <v>571885</v>
       </c>
-      <c r="N25" t="n">
+      <c r="V25" t="n">
         <v>847927</v>
       </c>
     </row>
@@ -1668,18 +2284,42 @@
         <v>145611.7510842763</v>
       </c>
       <c r="J26" t="n">
+        <v>6359.321285140562</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.023760958871355</v>
+      </c>
+      <c r="L26" t="n">
         <v>70131.54811710151</v>
       </c>
-      <c r="K26" t="n">
-        <v>0.009968740199935596</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.5512280881894932</v>
-      </c>
       <c r="M26" t="n">
+        <v>7269.65060240964</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.319858836216441</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.7566169727397398</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.005414302376183597</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.449857375811269</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7840242112037062</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.3334501623273732</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.554197100688249</v>
+      </c>
+      <c r="U26" t="n">
         <v>1630875</v>
       </c>
-      <c r="N26" t="n">
+      <c r="V26" t="n">
         <v>2610552</v>
       </c>
     </row>
@@ -1714,18 +2354,42 @@
         <v>123046.4970744207</v>
       </c>
       <c r="J27" t="n">
+        <v>5934.393574297189</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.037024964859788</v>
+      </c>
+      <c r="L27" t="n">
         <v>105943.3237173353</v>
       </c>
-      <c r="K27" t="n">
-        <v>0.02333457923205046</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.3699291500925386</v>
-      </c>
       <c r="M27" t="n">
+        <v>7929.261044176706</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8079522553270825</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8140266269669484</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.01214077052744952</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.133409461610464</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8146945738908031</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.2153093665838242</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.397671934280744</v>
+      </c>
+      <c r="U27" t="n">
         <v>1564631</v>
       </c>
-      <c r="N27" t="n">
+      <c r="V27" t="n">
         <v>2625081</v>
       </c>
     </row>
@@ -1760,25 +2424,49 @@
         <v>122686.9945617841</v>
       </c>
       <c r="J28" t="n">
+        <v>6352.831325301205</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.971491800433877</v>
+      </c>
+      <c r="L28" t="n">
         <v>98922.14818613917</v>
       </c>
-      <c r="K28" t="n">
-        <v>0.01555237078915874</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.3683375502232095</v>
-      </c>
       <c r="M28" t="n">
+        <v>7606.755020080322</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9517269856440966</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.7338116546577075</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.009157690812240948</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.818541278850268</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.7649568444446485</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2379853833805431</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.557042080650509</v>
+      </c>
+      <c r="U28" t="n">
         <v>1643529</v>
       </c>
-      <c r="N28" t="n">
+      <c r="V28" t="n">
         <v>2599858</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>mip_splatting</t>
+          <t>Mip-Splatting</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
@@ -1810,18 +2498,42 @@
         <v>1162.090006548799</v>
       </c>
       <c r="J29" t="n">
+        <v>136.2248995983936</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.4142778781145134</v>
+      </c>
+      <c r="L29" t="n">
         <v>1405.431138942913</v>
       </c>
-      <c r="K29" t="n">
-        <v>0.003159211971103672</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.3302009972637343</v>
-      </c>
       <c r="M29" t="n">
+        <v>137.4658634538153</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4154017749738699</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.963669722588137</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.002382759569269305</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.845351181435812</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.9305674900701874</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.2755300754155868</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.13797587957515</v>
+      </c>
+      <c r="U29" t="n">
         <v>36924</v>
       </c>
-      <c r="N29" t="n">
+      <c r="V29" t="n">
         <v>42121</v>
       </c>
     </row>
@@ -1856,18 +2568,42 @@
         <v>4867.512958027198</v>
       </c>
       <c r="J30" t="n">
+        <v>492.9879518072289</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.9335662312730317</v>
+      </c>
+      <c r="L30" t="n">
         <v>6379.115496090446</v>
       </c>
-      <c r="K30" t="n">
-        <v>0.006921164130764377</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.1913361462181694</v>
-      </c>
       <c r="M30" t="n">
+        <v>695.566265060241</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.028515007300646</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.9295079917204347</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.005085234233940189</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.00555316865293</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.7136559328727683</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1263252158056606</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.299635278398839</v>
+      </c>
+      <c r="U30" t="n">
         <v>145209</v>
       </c>
-      <c r="N30" t="n">
+      <c r="V30" t="n">
         <v>230607</v>
       </c>
     </row>
@@ -1902,18 +2638,42 @@
         <v>2831.864950208945</v>
       </c>
       <c r="J31" t="n">
+        <v>363.7670682730924</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.89329556876786</v>
+      </c>
+      <c r="L31" t="n">
         <v>2822.285061478668</v>
       </c>
-      <c r="K31" t="n">
-        <v>0.004794184841765056</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.2821478284601626</v>
-      </c>
       <c r="M31" t="n">
+        <v>357.281124497992</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9175182886035625</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.937363352908773</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.003535468681630763</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.089832722132904</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.874390862409824</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1451561119068753</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.049246076845745</v>
+      </c>
+      <c r="U31" t="n">
         <v>101490</v>
       </c>
-      <c r="N31" t="n">
+      <c r="V31" t="n">
         <v>101310</v>
       </c>
     </row>
@@ -1948,18 +2708,42 @@
         <v>6161.04677654858</v>
       </c>
       <c r="J32" t="n">
+        <v>586.6265060240963</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8623783395611029</v>
+      </c>
+      <c r="L32" t="n">
         <v>21863.2883386156</v>
       </c>
-      <c r="K32" t="n">
-        <v>0.003458551208890693</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.2721999471266155</v>
-      </c>
       <c r="M32" t="n">
+        <v>1222.088353413655</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5302633442240808</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9694859804139654</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.002479640476075568</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.964670967503665</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9652826733642501</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.2380210886468414</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.31073923080196</v>
+      </c>
+      <c r="U32" t="n">
         <v>153555</v>
       </c>
-      <c r="N32" t="n">
+      <c r="V32" t="n">
         <v>453116</v>
       </c>
     </row>
@@ -1994,18 +2778,42 @@
         <v>12601.90173232002</v>
       </c>
       <c r="J33" t="n">
+        <v>1256.132530120482</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.3470777870010379</v>
+      </c>
+      <c r="L33" t="n">
         <v>28352.88307316839</v>
       </c>
-      <c r="K33" t="n">
-        <v>0.007362207998475028</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.1485181953546982</v>
-      </c>
       <c r="M33" t="n">
+        <v>2015.634538152611</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8549863522734902</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9684368082545979</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.00561364124190401</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.705741015090209</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.9485730591824477</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.1126453808762811</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.030658594547198</v>
+      </c>
+      <c r="U33" t="n">
         <v>359624</v>
       </c>
-      <c r="N33" t="n">
+      <c r="V33" t="n">
         <v>739048</v>
       </c>
     </row>
@@ -2040,18 +2848,42 @@
         <v>10118.70065892932</v>
       </c>
       <c r="J34" t="n">
+        <v>1047.859437751004</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8757198871886192</v>
+      </c>
+      <c r="L34" t="n">
         <v>23278.64021014351</v>
       </c>
-      <c r="K34" t="n">
-        <v>0.005755266700393787</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.1877566583066714</v>
-      </c>
       <c r="M34" t="n">
+        <v>1842.638554216868</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8889220055822168</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.956748988062872</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.003863279474899173</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.066239978949756</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.9403401450613801</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.1330125365744937</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.973881373939914</v>
+      </c>
+      <c r="U34" t="n">
         <v>277536</v>
       </c>
-      <c r="N34" t="n">
+      <c r="V34" t="n">
         <v>553487</v>
       </c>
     </row>
@@ -2086,18 +2918,42 @@
         <v>20637.29970390002</v>
       </c>
       <c r="J35" t="n">
+        <v>1872.831325301205</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.2889418953082999</v>
+      </c>
+      <c r="L35" t="n">
         <v>39461.46235903824</v>
       </c>
-      <c r="K35" t="n">
-        <v>0.002964374774058101</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.2437199981023697</v>
-      </c>
       <c r="M35" t="n">
+        <v>3740.698795180723</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.38202308897477</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9828507024473697</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.002535158173465481</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.064774315376621</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.9757359479361436</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2365821224826199</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.405662511627839</v>
+      </c>
+      <c r="U35" t="n">
         <v>503528</v>
       </c>
-      <c r="N35" t="n">
+      <c r="V35" t="n">
         <v>1483745</v>
       </c>
     </row>
@@ -2132,18 +2988,42 @@
         <v>27986.66686470916</v>
       </c>
       <c r="J36" t="n">
+        <v>2567.024096385542</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.1837474536109679</v>
+      </c>
+      <c r="L36" t="n">
         <v>81018.5987976835</v>
       </c>
-      <c r="K36" t="n">
-        <v>0.006920365822731298</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.1306360718491562</v>
-      </c>
       <c r="M36" t="n">
+        <v>6017.024096385542</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.9563880798490482</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9837861435053699</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.006058553741736846</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.73654336209709</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.9779907017977827</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.1146827421405099</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.334181301517623</v>
+      </c>
+      <c r="U36" t="n">
         <v>711073</v>
       </c>
-      <c r="N36" t="n">
+      <c r="V36" t="n">
         <v>1771279</v>
       </c>
     </row>
@@ -2178,25 +3058,49 @@
         <v>31666.80418572111</v>
       </c>
       <c r="J37" t="n">
+        <v>2605.678714859438</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.2341808944126401</v>
+      </c>
+      <c r="L37" t="n">
         <v>63201.34574765692</v>
       </c>
-      <c r="K37" t="n">
-        <v>0.005452265469973845</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.1489633650649207</v>
-      </c>
       <c r="M37" t="n">
+        <v>4491.080321285141</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.6430453737929496</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.9714668169599022</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.004027465210211548</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.846074553462729</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.9743004515914409</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.1430124789476395</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.192996430771753</v>
+      </c>
+      <c r="U37" t="n">
         <v>675644</v>
       </c>
-      <c r="N37" t="n">
+      <c r="V37" t="n">
         <v>1632565</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>eagles</t>
+          <t>EAGLES</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
@@ -2228,18 +3132,42 @@
         <v>2482.931786568032</v>
       </c>
       <c r="J38" t="n">
+        <v>241.8514056224899</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.012105358778422</v>
+      </c>
+      <c r="L38" t="n">
         <v>2468.734009542164</v>
       </c>
-      <c r="K38" t="n">
-        <v>0.003415236729043468</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.354544160483056</v>
-      </c>
       <c r="M38" t="n">
+        <v>232.136546184739</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.451209925578209</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.952891170495302</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.002754744428854675</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.756307284037496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.8907973920938268</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.2458792799836274</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.91518988488855</v>
+      </c>
+      <c r="U38" t="n">
         <v>77938</v>
       </c>
-      <c r="N38" t="n">
+      <c r="V38" t="n">
         <v>66340</v>
       </c>
     </row>
@@ -2274,18 +3202,42 @@
         <v>5674.409336569927</v>
       </c>
       <c r="J39" t="n">
+        <v>595.3172690763053</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.6293288549993538</v>
+      </c>
+      <c r="L39" t="n">
         <v>7233.061430511575</v>
       </c>
-      <c r="K39" t="n">
-        <v>0.005428582118528747</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.1561589692728718</v>
-      </c>
       <c r="M39" t="n">
+        <v>724.2208835341365</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.9924873884625838</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9442954214515116</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.004333960823714733</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.208349319679159</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.7013500829324879</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.1172997870228507</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.300438560098002</v>
+      </c>
+      <c r="U39" t="n">
         <v>186269</v>
       </c>
-      <c r="N39" t="n">
+      <c r="V39" t="n">
         <v>254987</v>
       </c>
     </row>
@@ -2320,18 +3272,42 @@
         <v>3473.297791656879</v>
       </c>
       <c r="J40" t="n">
+        <v>391.7028112449799</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.9202520546964023</v>
+      </c>
+      <c r="L40" t="n">
         <v>3457.186605257728</v>
       </c>
-      <c r="K40" t="n">
-        <v>0.004756535825812099</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.2581086274944709</v>
-      </c>
       <c r="M40" t="n">
+        <v>325.281124497992</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.821070965331123</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.939185120516522</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.003315966661003503</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.949465483509579</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.8484877025222579</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.1432284699244933</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.937356083757097</v>
+      </c>
+      <c r="U40" t="n">
         <v>121170</v>
       </c>
-      <c r="N40" t="n">
+      <c r="V40" t="n">
         <v>104213</v>
       </c>
     </row>
@@ -2366,18 +3342,42 @@
         <v>10749.43712746848</v>
       </c>
       <c r="J41" t="n">
+        <v>1110.409638554217</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.9032201733998193</v>
+      </c>
+      <c r="L41" t="n">
         <v>20274.7396509122</v>
       </c>
-      <c r="K41" t="n">
-        <v>0.003210300430701096</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.2536984249146489</v>
-      </c>
       <c r="M41" t="n">
+        <v>1513.586345381526</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.6607662934445033</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.9733300696693244</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.002725337178279335</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.703206605099392</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9670622612966221</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.2665568487349648</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.231702536817328</v>
+      </c>
+      <c r="U41" t="n">
         <v>310287</v>
       </c>
-      <c r="N41" t="n">
+      <c r="V41" t="n">
         <v>551003</v>
       </c>
     </row>
@@ -2412,18 +3412,42 @@
         <v>18921.00726027183</v>
       </c>
       <c r="J42" t="n">
+        <v>1880.967871485944</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9862159958816302</v>
+      </c>
+      <c r="L42" t="n">
         <v>29001.97770617394</v>
       </c>
-      <c r="K42" t="n">
-        <v>0.004985898535429137</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.102586215934477</v>
-      </c>
       <c r="M42" t="n">
+        <v>2910.807228915663</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.166199556544158</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9853803372926128</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.005218383919616992</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.976526148185334</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9739323983095793</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.1115165623751554</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.480238271356338</v>
+      </c>
+      <c r="U42" t="n">
         <v>524010</v>
       </c>
-      <c r="N42" t="n">
+      <c r="V42" t="n">
         <v>844823</v>
       </c>
     </row>
@@ -2458,18 +3482,42 @@
         <v>15221.54537262694</v>
       </c>
       <c r="J43" t="n">
+        <v>1629.883534136546</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.948769415201372</v>
+      </c>
+      <c r="L43" t="n">
         <v>24314.75465713838</v>
       </c>
-      <c r="K43" t="n">
-        <v>0.005301287130875213</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.1602060329575174</v>
-      </c>
       <c r="M43" t="n">
+        <v>2154.658634538152</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.4372064571065133</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9657367373913517</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.003788319395177743</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.915655712044591</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.9574262561893597</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.1268104253844781</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.069866334863942</v>
+      </c>
+      <c r="U43" t="n">
         <v>464581</v>
       </c>
-      <c r="N43" t="n">
+      <c r="V43" t="n">
         <v>681783</v>
       </c>
     </row>
@@ -2504,18 +3552,42 @@
         <v>30527.23756059921</v>
       </c>
       <c r="J44" t="n">
+        <v>3073.497991967872</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.7633755347992728</v>
+      </c>
+      <c r="L44" t="n">
         <v>37278.16706978124</v>
       </c>
-      <c r="K44" t="n">
-        <v>0.003012004228806005</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.2560405261484828</v>
-      </c>
       <c r="M44" t="n">
+        <v>4594.156626506024</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.77894795283432</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9800192909129585</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.002485051664300151</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.957737991134526</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.97061612902362</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.2404705955709886</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.172298531448756</v>
+      </c>
+      <c r="U44" t="n">
         <v>891304</v>
       </c>
-      <c r="N44" t="n">
+      <c r="V44" t="n">
         <v>1715377</v>
       </c>
     </row>
@@ -2550,18 +3622,42 @@
         <v>47762.09721952032</v>
       </c>
       <c r="J45" t="n">
+        <v>4608.012048192771</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.9972248284807406</v>
+      </c>
+      <c r="L45" t="n">
         <v>91702.0888860103</v>
       </c>
-      <c r="K45" t="n">
-        <v>0.004330094265729711</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.08405743851022202</v>
-      </c>
       <c r="M45" t="n">
+        <v>5881.658634538153</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.7987541954066041</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.9933339792870969</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.005624362775547938</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.048457473394604</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.9903186607261165</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.1207245276732878</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.562722124601937</v>
+      </c>
+      <c r="U45" t="n">
         <v>1215459</v>
       </c>
-      <c r="N45" t="n">
+      <c r="V45" t="n">
         <v>2119820</v>
       </c>
     </row>
@@ -2596,25 +3692,49 @@
         <v>54346.55470743151</v>
       </c>
       <c r="J46" t="n">
+        <v>4980.871485943775</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.8397248157616827</v>
+      </c>
+      <c r="L46" t="n">
         <v>69443.21437125778</v>
       </c>
-      <c r="K46" t="n">
-        <v>0.004751541675132578</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.128278526228736</v>
-      </c>
       <c r="M46" t="n">
+        <v>6389.530120481928</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.020216509832284</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.979745325251471</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.004125105005434968</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.961363654018054</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.9812890641207366</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.1442972225221721</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.348877903415056</v>
+      </c>
+      <c r="U46" t="n">
         <v>1342104</v>
       </c>
-      <c r="N46" t="n">
+      <c r="V46" t="n">
         <v>2142862</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>gaussian_pro</t>
+          <t>Gaussian-Pro</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
@@ -2646,18 +3766,42 @@
         <v>1264.179029099233</v>
       </c>
       <c r="J47" t="n">
+        <v>139.6506024096386</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.4238139503180577</v>
+      </c>
+      <c r="L47" t="n">
         <v>1476.093187397266</v>
       </c>
-      <c r="K47" t="n">
-        <v>0.003287101124670411</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.3682403274100838</v>
-      </c>
       <c r="M47" t="n">
+        <v>159.293172690763</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.7474202947201818</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.9588239949896457</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.002724764699285681</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.71845751406971</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.9232669829491187</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.2818838449624866</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.329914286135826</v>
+      </c>
+      <c r="U47" t="n">
         <v>37993</v>
       </c>
-      <c r="N47" t="n">
+      <c r="V47" t="n">
         <v>43182</v>
       </c>
     </row>
@@ -2692,18 +3836,42 @@
         <v>4892.016710049714</v>
       </c>
       <c r="J48" t="n">
+        <v>489.2208835341365</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.8806677844298572</v>
+      </c>
+      <c r="L48" t="n">
         <v>6266.181377881462</v>
       </c>
-      <c r="K48" t="n">
-        <v>0.00557088942345717</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.1798461998837823</v>
-      </c>
       <c r="M48" t="n">
+        <v>678.3895582329317</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.7852874365797753</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9511295240997596</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.004533874378962951</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.066594710274224</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.8280341251419892</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.1232840364629572</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.202651995703726</v>
+      </c>
+      <c r="U48" t="n">
         <v>146931</v>
       </c>
-      <c r="N48" t="n">
+      <c r="V48" t="n">
         <v>232412</v>
       </c>
     </row>
@@ -2738,18 +3906,42 @@
         <v>2856.097135811186</v>
       </c>
       <c r="J49" t="n">
+        <v>412.3012048192771</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.4938470992799194</v>
+      </c>
+      <c r="L49" t="n">
         <v>2836.252428673133</v>
       </c>
-      <c r="K49" t="n">
-        <v>0.005017686676878083</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.2762278192017751</v>
-      </c>
       <c r="M49" t="n">
+        <v>410.3855421686747</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.5689673690734909</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.93727056234595</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.003680912608450109</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.83138841250715</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.8746618110010075</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.1729901412671263</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.00468868655271</v>
+      </c>
+      <c r="U49" t="n">
         <v>112144</v>
       </c>
-      <c r="N49" t="n">
+      <c r="V49" t="n">
         <v>111921</v>
       </c>
     </row>
@@ -2784,18 +3976,42 @@
         <v>6752.163524766376</v>
       </c>
       <c r="J50" t="n">
+        <v>656.9558232931727</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.5888698280635233</v>
+      </c>
+      <c r="L50" t="n">
         <v>18282.26421488323</v>
       </c>
-      <c r="K50" t="n">
-        <v>0.003151870595110263</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.2733445602927124</v>
-      </c>
       <c r="M50" t="n">
+        <v>1561.923694779116</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.085022909873807</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.9723082540933387</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.002654511820186268</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.018916007292462</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.9613722559739718</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.2782212976531265</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.226712566810885</v>
+      </c>
+      <c r="U50" t="n">
         <v>175317</v>
       </c>
-      <c r="N50" t="n">
+      <c r="V50" t="n">
         <v>474827</v>
       </c>
     </row>
@@ -2830,18 +4046,42 @@
         <v>15349.22007376121</v>
       </c>
       <c r="J51" t="n">
+        <v>1456.305220883534</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.8227440934423574</v>
+      </c>
+      <c r="L51" t="n">
         <v>26574.39898621709</v>
       </c>
-      <c r="K51" t="n">
-        <v>0.005462037709993835</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.1186877293042907</v>
-      </c>
       <c r="M51" t="n">
+        <v>2807.461847389558</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.095000287661952</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9809114300063584</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.005295296622948213</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.354821764419021</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9617390354622358</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.1147143583406102</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.532187134450199</v>
+      </c>
+      <c r="U51" t="n">
         <v>407824</v>
       </c>
-      <c r="N51" t="n">
+      <c r="V51" t="n">
         <v>787349</v>
       </c>
     </row>
@@ -2876,18 +4116,42 @@
         <v>13996.54121292391</v>
       </c>
       <c r="J52" t="n">
+        <v>1313.088353413655</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.8844128203290391</v>
+      </c>
+      <c r="L52" t="n">
         <v>22367.91312482219</v>
       </c>
-      <c r="K52" t="n">
-        <v>0.005247736756673754</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.1752723730207706</v>
-      </c>
       <c r="M52" t="n">
+        <v>1752.429718875502</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.045489419511556</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.9643284147529745</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.004105830057100816</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.034050237699757</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.9441086007375108</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.1638536256822673</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.378119600758741</v>
+      </c>
+      <c r="U52" t="n">
         <v>346894</v>
       </c>
-      <c r="N52" t="n">
+      <c r="V52" t="n">
         <v>622788</v>
       </c>
     </row>
@@ -2922,18 +4186,42 @@
         <v>19573.38564624444</v>
       </c>
       <c r="J53" t="n">
+        <v>2036.152610441767</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.2133596277827385</v>
+      </c>
+      <c r="L53" t="n">
         <v>26526.91193957526</v>
       </c>
-      <c r="K53" t="n">
-        <v>0.002949135252250628</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.2188888620373097</v>
-      </c>
       <c r="M53" t="n">
+        <v>4353.293172690763</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.823307026173039</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.9806384775954982</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.002459159628911452</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.976033813188865</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.9773985214745976</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.2141969137258459</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.439629227351716</v>
+      </c>
+      <c r="U53" t="n">
         <v>573029</v>
       </c>
-      <c r="N53" t="n">
+      <c r="V53" t="n">
         <v>1552840</v>
       </c>
     </row>
@@ -2968,18 +4256,42 @@
         <v>42703.16946630965</v>
       </c>
       <c r="J54" t="n">
+        <v>3704.562248995984</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.8401885950986079</v>
+      </c>
+      <c r="L54" t="n">
         <v>91006.42687462237</v>
       </c>
-      <c r="K54" t="n">
-        <v>0.004788893660383182</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.09581433123006639</v>
-      </c>
       <c r="M54" t="n">
+        <v>6305.522088353414</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.285304236657652</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.9921373495512956</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.00579655339772051</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.508389697428237</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9872792167334808</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.1222356991334395</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.754415189958358</v>
+      </c>
+      <c r="U54" t="n">
         <v>989297</v>
       </c>
-      <c r="N54" t="n">
+      <c r="V54" t="n">
         <v>2049451</v>
       </c>
     </row>
@@ -3014,25 +4326,49 @@
         <v>45561.73453329534</v>
       </c>
       <c r="J55" t="n">
+        <v>3873.341365461848</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.8692046467673107</v>
+      </c>
+      <c r="L55" t="n">
         <v>63237.28581070426</v>
       </c>
-      <c r="K55" t="n">
-        <v>0.0046331890899772</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.1499347648720463</v>
-      </c>
       <c r="M55" t="n">
+        <v>5650.437751004016</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8508455648782671</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.9803176815215475</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.004509811374274167</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.084770683093367</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.9735873549921273</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.1813529201529243</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.503760987692844</v>
+      </c>
+      <c r="U55" t="n">
         <v>1016671</v>
       </c>
-      <c r="N55" t="n">
+      <c r="V55" t="n">
         <v>1973075</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>geo_gaussian</t>
+          <t>Geo-Gaussian</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
@@ -3064,18 +4400,42 @@
         <v>2659.556605405725</v>
       </c>
       <c r="J56" t="n">
+        <v>343.437751004016</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5990211655916707</v>
+      </c>
+      <c r="L56" t="n">
         <v>2821.661793242916</v>
       </c>
-      <c r="K56" t="n">
-        <v>0.01435288726084649</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.6087547068453586</v>
-      </c>
       <c r="M56" t="n">
+        <v>356.4096385542169</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.6670341225817599</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8675670304063025</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.004864156923510812</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.127546218566178</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.9305996217523886</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.3071981296116936</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.427010017098705</v>
+      </c>
+      <c r="U56" t="n">
         <v>112392</v>
       </c>
-      <c r="N56" t="n">
+      <c r="V56" t="n">
         <v>117363</v>
       </c>
     </row>
@@ -3110,18 +4470,42 @@
         <v>5099.712992699749</v>
       </c>
       <c r="J57" t="n">
+        <v>607.9156626506024</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.8710195115537356</v>
+      </c>
+      <c r="L57" t="n">
         <v>8515.612616770433</v>
       </c>
-      <c r="K57" t="n">
-        <v>0.004641510234916834</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.1690693174120478</v>
-      </c>
       <c r="M57" t="n">
+        <v>797.3855421686746</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.025723662300021</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.9860177264310824</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.003895114768635143</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.299024822633087</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.951915936442397</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.1299538354982029</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.280062249579023</v>
+      </c>
+      <c r="U57" t="n">
         <v>178383</v>
       </c>
-      <c r="N57" t="n">
+      <c r="V57" t="n">
         <v>263550</v>
       </c>
     </row>
@@ -3156,18 +4540,42 @@
         <v>3748.407470228135</v>
       </c>
       <c r="J58" t="n">
+        <v>401.2128514056225</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.5123692891735341</v>
+      </c>
+      <c r="L58" t="n">
         <v>3705.546183862782</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.006330226200919118</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0.3217338661905865</v>
-      </c>
       <c r="M58" t="n">
+        <v>427.144578313253</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.7372412875727121</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.9539048467196382</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.003273073922504078</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.813027038757483</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.8951105565039179</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.1351237987930125</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.0431542280839</v>
+      </c>
+      <c r="U58" t="n">
         <v>123434</v>
       </c>
-      <c r="N58" t="n">
+      <c r="V58" t="n">
         <v>122885</v>
       </c>
     </row>
@@ -3202,18 +4610,42 @@
         <v>16012.69859769139</v>
       </c>
       <c r="J59" t="n">
+        <v>1826.212851405623</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.7791355020130286</v>
+      </c>
+      <c r="L59" t="n">
         <v>18236.93924993191</v>
       </c>
-      <c r="K59" t="n">
-        <v>0.01401405920554537</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.5809566569057665</v>
-      </c>
       <c r="M59" t="n">
+        <v>2345.317269076305</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.183312285051067</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8928835366211539</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.005066435445438732</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.095685692798252</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9467764877930637</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.3295298439639434</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.773913595453537</v>
+      </c>
+      <c r="U59" t="n">
         <v>602096</v>
       </c>
-      <c r="N59" t="n">
+      <c r="V59" t="n">
         <v>899439</v>
       </c>
     </row>
@@ -3248,18 +4680,42 @@
         <v>23660.23601622508</v>
       </c>
       <c r="J60" t="n">
+        <v>2139.690763052209</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.6553989386552954</v>
+      </c>
+      <c r="L60" t="n">
         <v>38645.58594481412</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.005610532073251591</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.1618247149528569</v>
-      </c>
       <c r="M60" t="n">
+        <v>2916.955823293173</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.332889141414771</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.9924976183122312</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.005291828377680345</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.326613774398688</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.9801924963215166</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.1369412961331281</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.247845320625101</v>
+      </c>
+      <c r="U60" t="n">
         <v>649331</v>
       </c>
-      <c r="N60" t="n">
+      <c r="V60" t="n">
         <v>1027102</v>
       </c>
     </row>
@@ -3294,18 +4750,42 @@
         <v>13426.91728413149</v>
       </c>
       <c r="J61" t="n">
+        <v>1657.469879518072</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.6864697549492363</v>
+      </c>
+      <c r="L61" t="n">
         <v>25176.38281717443</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.006772848923502968</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.2915994441173307</v>
-      </c>
       <c r="M61" t="n">
+        <v>2364.674698795181</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.6941809120838723</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.9651733756570867</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.003800531002608212</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.30938850188425</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.9418021503939031</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.1483810452575034</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.276043542956983</v>
+      </c>
+      <c r="U61" t="n">
         <v>503168</v>
       </c>
-      <c r="N61" t="n">
+      <c r="V61" t="n">
         <v>777267</v>
       </c>
     </row>
@@ -3340,18 +4820,42 @@
         <v>32721.27440580566</v>
       </c>
       <c r="J62" t="n">
+        <v>3612.951807228916</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.659415002912323</v>
+      </c>
+      <c r="L62" t="n">
         <v>29477.5732004514</v>
       </c>
-      <c r="K62" t="n">
-        <v>0.01417720673821209</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.5940247026474864</v>
-      </c>
       <c r="M62" t="n">
+        <v>4811.542168674699</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.494042191934493</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8967846874312135</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.004950576207854531</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.9708456287906799</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.9473274304500563</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.3093757337623542</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.404292459772114</v>
+      </c>
+      <c r="U62" t="n">
         <v>1078531</v>
       </c>
-      <c r="N62" t="n">
+      <c r="V62" t="n">
         <v>1613172</v>
       </c>
     </row>
@@ -3386,18 +4890,42 @@
         <v>65124.89584302092</v>
       </c>
       <c r="J63" t="n">
+        <v>4293.236947791164</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.5792332944003649</v>
+      </c>
+      <c r="L63" t="n">
         <v>73536.31567497655</v>
       </c>
-      <c r="K63" t="n">
-        <v>0.004539515281063416</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.1474689196964982</v>
-      </c>
       <c r="M63" t="n">
+        <v>5927.096385542169</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1.339121466140099</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9968701463687131</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.005316156555305828</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.13997039615423</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.9868066430110463</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.1312905312939123</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.128415593085561</v>
+      </c>
+      <c r="U63" t="n">
         <v>1313383</v>
       </c>
-      <c r="N63" t="n">
+      <c r="V63" t="n">
         <v>2141518</v>
       </c>
     </row>
@@ -3432,18 +4960,42 @@
         <v>56088.88261583029</v>
       </c>
       <c r="J64" t="n">
+        <v>5691.333333333333</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.730859157088473</v>
+      </c>
+      <c r="L64" t="n">
         <v>52460.03174275792</v>
       </c>
-      <c r="K64" t="n">
-        <v>0.006028384609768099</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0.2513956653709438</v>
-      </c>
       <c r="M64" t="n">
+        <v>7224.184738955823</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1.402640496905352</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.9788864939844198</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.004076542502099817</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.498552398438694</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.9677527933710701</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.1521106524900957</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.82335496656324</v>
+      </c>
+      <c r="U64" t="n">
         <v>1831222</v>
       </c>
-      <c r="N64" t="n">
+      <c r="V64" t="n">
         <v>2775854</v>
       </c>
     </row>
